--- a/list2.xlsx
+++ b/list2.xlsx
@@ -414,32 +414,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N001001140</t>
+          <t>N011B1BARN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>URMC-STRONG MEMORIAL HOSPITAL</t>
+          <t>BARNES-JEWISH HOSPITAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>575 ELMWOOD AVE RM 30852</t>
+          <t>1 BARNES-JEWISH HOSPITAL PLAZA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ROCHESTER</t>
+          <t>SAINT LOUIS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -453,44 +453,44 @@
         </is>
       </c>
       <c r="I2">
-        <v>886</v>
+        <v>1431</v>
       </c>
       <c r="J2">
-        <v>47521</v>
+        <v>38697</v>
       </c>
       <c r="K2">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N001003102</t>
+          <t>N016COL012</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GUTHRIE LOURDES HOSPITAL</t>
+          <t>OHIO STATE UNIVERSITY WEXNER MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASCENSION HLTH MINISTRY SRV CT</t>
+          <t>410 W 10TH AVE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS</t>
+          <t>COLUMBUS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46203</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -504,49 +504,49 @@
         </is>
       </c>
       <c r="I3">
-        <v>242</v>
+        <v>1106</v>
       </c>
       <c r="J3">
-        <v>18194</v>
+        <v>24860</v>
       </c>
       <c r="K3">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N001B1AMCH</t>
+          <t>N053B0HOPK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALBANY MEDICAL CENTER HOSPITAL</t>
+          <t>JOHNS HOPKINS HOSPITAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43 NEW SCOTLAND AVENUE</t>
+          <t>PO BOX 5085</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALBANY</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -555,44 +555,44 @@
         </is>
       </c>
       <c r="I4">
-        <v>748</v>
+        <v>1095</v>
       </c>
       <c r="J4">
-        <v>27589</v>
+        <v>58423</v>
       </c>
       <c r="K4">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N0031135</t>
+          <t>N0041039</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCA-MEMORIAL MEDICAL CENTER</t>
+          <t>MASSACHUSETTS GENERAL HOSPITAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4700 WATERS AVE</t>
+          <t>55 FRUIT STREET</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAVANNAH</t>
+          <t>BOSTON</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31404-6220</t>
+          <t>02114</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,44 +606,44 @@
         </is>
       </c>
       <c r="I5">
-        <v>512</v>
+        <v>1043</v>
       </c>
       <c r="J5">
-        <v>22050</v>
+        <v>39730</v>
       </c>
       <c r="K5">
-        <v>0.21</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N003B1KENN</t>
+          <t>N019058000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WELLSTAR KENNESTONE HOSPITAL</t>
+          <t>VANDERBILT UNIVERSITY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>677 CHURCH STREET</t>
+          <t>1301 MEDICAL CENTER DRIVE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARIETTA</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,95 +657,95 @@
         </is>
       </c>
       <c r="I6">
-        <v>633</v>
+        <v>1025</v>
       </c>
       <c r="J6">
-        <v>24159</v>
+        <v>50744</v>
       </c>
       <c r="K6">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N003B1SRMC</t>
+          <t>N013B5UMMC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOUTHERN REGIONAL MEDICAL CENTER</t>
+          <t>UNIVERSITY OF MICHIGAN HOSPITALS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3480 E GUASTI ROAD 2ND FLOOR</t>
+          <t>1500 EAST MEDICAL CENTER DR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ONTARIO</t>
+          <t>ANN ARBOR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91761</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I7">
-        <v>331</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>8193</v>
+        <v>35336</v>
       </c>
       <c r="K7">
-        <v>1.53</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N003B4MCMA</t>
+          <t>N0122225</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATRIUM HEALTH NAVICENT</t>
+          <t>DUMC DUKE UNIVERSITY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>777 HEMLOCK STREET</t>
+          <t>2301 ERWIN ROAD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MACON</t>
+          <t>DURHAM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -759,44 +759,44 @@
         </is>
       </c>
       <c r="I8">
-        <v>637</v>
+        <v>960</v>
       </c>
       <c r="J8">
-        <v>24828</v>
+        <v>38334</v>
       </c>
       <c r="K8">
-        <v>1.81</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N003B6PMID</t>
+          <t>N053B1WAHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PIEDMONT COLUMBUS REGIONAL MIDTOWN HOSP</t>
+          <t>WASHINGTON HOSPITAL CENTER</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>710 CENTER STREET</t>
+          <t>C/O MEDSTAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COLUMBUS</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>21236-6200</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -810,44 +810,44 @@
         </is>
       </c>
       <c r="I9">
-        <v>583</v>
+        <v>926</v>
       </c>
       <c r="J9">
-        <v>11941</v>
+        <v>23505</v>
       </c>
       <c r="K9">
-        <v>0.4</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N0041039</t>
+          <t>N0122425</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS GENERAL HOSPITAL</t>
+          <t>UNC MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>55 FRUIT STREET</t>
+          <t>101 MANNING DRIVE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOSTON</t>
+          <t>CHAPEL HILL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02114</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -861,34 +861,34 @@
         </is>
       </c>
       <c r="I10">
-        <v>1043</v>
+        <v>923</v>
       </c>
       <c r="J10">
-        <v>39730</v>
+        <v>30184</v>
       </c>
       <c r="K10">
-        <v>1.12</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N0042003</t>
+          <t>N049T0062C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VA MEDICAL CENTER WEST ROXBURY</t>
+          <t>BAYLOR UNIVERSITY MEDICAL CTR AT DALLAS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEPT OF VETERANS AFFAIRS</t>
+          <t>3500 GASTON AVENUE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AUSTIN</t>
+          <t>DALLAS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>78714-9975</t>
+          <t>75246</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -908,45 +908,48 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I11">
-        <v>172</v>
+        <v>914</v>
+      </c>
+      <c r="J11">
+        <v>20997</v>
       </c>
       <c r="K11">
-        <v>0.28</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N0047128</t>
+          <t>N022XWC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF VERMONT MEDICAL CENTER</t>
+          <t>CHRISTIANA CARE HEALTH SERVICES, INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>111 COLCHESTER AVENUE</t>
+          <t>PO BOX 2653</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BURLINGTON</t>
+          <t>WILMINGTON</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05401</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -960,44 +963,41 @@
         </is>
       </c>
       <c r="I12">
-        <v>562</v>
-      </c>
-      <c r="J12">
-        <v>22255</v>
+        <v>906</v>
       </c>
       <c r="K12">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N0047369</t>
+          <t>N001001140</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCA-PORTSMOUTH HOSPITAL</t>
+          <t>URMC-STRONG MEMORIAL HOSPITAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>333 BORTHWICK AVENUE</t>
+          <t>575 ELMWOOD AVE RM 30852</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PORTSMOUTH</t>
+          <t>ROCHESTER</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>03801</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1011,151 +1011,151 @@
         </is>
       </c>
       <c r="I13">
-        <v>220</v>
+        <v>886</v>
       </c>
       <c r="J13">
-        <v>12274</v>
+        <v>47521</v>
       </c>
       <c r="K13">
-        <v>0.76</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N006B0COLA</t>
+          <t>N035N1VCU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LOS ANGELES COMMUNITY HOSPITAL</t>
+          <t>VCU MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4081 EAST OLYMPIC BLVD</t>
+          <t>800 EAST LEIGH STREET STE 212</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>RICHMOND</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14">
-        <v>91</v>
+        <v>811</v>
       </c>
       <c r="J14">
-        <v>1360</v>
+        <v>28758</v>
       </c>
       <c r="K14">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N006B3HUWA</t>
+          <t>N040B0ADVC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WEST ANAHEIM MEDICAL CENTER</t>
+          <t>ADVOCATE CHRIST MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3033 WEST ORANGE AVENUE</t>
+          <t>4440 W 95TH ST</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ANAHEIM</t>
+          <t>OAK LAWN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I15">
-        <v>219</v>
+        <v>802</v>
       </c>
       <c r="J15">
-        <v>1077</v>
+        <v>21518</v>
       </c>
       <c r="K15">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N006B3UCIM</t>
+          <t>N0122415</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF CALIFORNIA, IRVINE MEDICAL CENTER</t>
+          <t>NEW HANOVER REGIONAL MED CTR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PO BOX C11917</t>
+          <t>PO BOX 1649</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>WILMINGTON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92711</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1164,44 +1164,44 @@
         </is>
       </c>
       <c r="I16">
-        <v>418</v>
+        <v>800</v>
       </c>
       <c r="J16">
-        <v>12748</v>
+        <v>28039</v>
       </c>
       <c r="K16">
-        <v>1.74</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N006B9RRMC</t>
+          <t>N016COL013</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RONALD REAGAN UCLA MEDICAL CENTER</t>
+          <t>RIVERSIDE METHODIST HOSPITAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>757 WESTWOOD BLVD</t>
+          <t>3535 OLENTANGY RIVER RD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>COLUMBUS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>43214</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1215,44 +1215,44 @@
         </is>
       </c>
       <c r="I17">
-        <v>446</v>
+        <v>786</v>
       </c>
       <c r="J17">
-        <v>23644</v>
+        <v>21606</v>
       </c>
       <c r="K17">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N006BJANVD</t>
+          <t>N020LVSHMC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANTELOPE VALLEY MEDICAL CENTER</t>
+          <t>SUNRISE HOSPITAL &amp; MED CTR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1600 WEST AVENUE J</t>
+          <t>3186 SOUTH MARYLAND PKWY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LANCASTER</t>
+          <t>LAS VEGAS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93534</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1266,194 +1266,197 @@
         </is>
       </c>
       <c r="I18">
-        <v>390</v>
+        <v>762</v>
       </c>
       <c r="J18">
-        <v>12259</v>
+        <v>17255</v>
       </c>
       <c r="K18">
-        <v>0.83</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N006BNCEVC</t>
+          <t>N001B1AMCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CENTINELA HOSPITAL MEDICAL CENTER</t>
+          <t>ALBANY MEDICAL CENTER HOSPITAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>555 EAST HARDY STREET</t>
+          <t>43 NEW SCOTLAND AVENUE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>INGLEWOOD</t>
+          <t>ALBANY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>90301</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I19">
-        <v>362</v>
+        <v>748</v>
       </c>
       <c r="J19">
-        <v>2035</v>
+        <v>27589</v>
       </c>
       <c r="K19">
-        <v>0.03</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N006BZKONT</t>
+          <t>N035CCLB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KAISER PERMANENTE ONTARIO MED CTR</t>
+          <t>CARILION CONSOLIDATED LABS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2295 SOUTH VINEYARD AVENUE</t>
+          <t>PO BOX 13367</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ONTARIO</t>
+          <t>ROANOKE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>91761</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I20">
-        <v>224</v>
+        <v>737</v>
       </c>
       <c r="J20">
-        <v>17033</v>
+        <v>25834</v>
       </c>
       <c r="K20">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N006BZPKVW</t>
+          <t>N022TEM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DOCTORS HOSPITAL OF RIVERSIDE</t>
+          <t>TEMPLE UNIVERSITY HOSPITAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3865 JACKSON ST</t>
+          <t>3401 N BROAD STREET</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RIVERSIDE</t>
+          <t>PHILADELPHIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>92503</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I21">
-        <v>193</v>
+        <v>732</v>
+      </c>
+      <c r="J21">
+        <v>30008</v>
       </c>
       <c r="K21">
-        <v>0.07000000000000001</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N006BZRIVE</t>
+          <t>N036B1MUSC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RIVERSIDE COMMUNITY HOSPITAL</t>
+          <t>MEDICAL UNIVERSITY OF SC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PO BOX 788</t>
+          <t>MUSC HEMAPHERESIS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAYSVILLE</t>
+          <t>CHARLESTON</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>84037</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1467,44 +1470,44 @@
         </is>
       </c>
       <c r="I22">
-        <v>478</v>
+        <v>713</v>
       </c>
       <c r="J22">
-        <v>7760</v>
+        <v>36299</v>
       </c>
       <c r="K22">
-        <v>0.68</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N006E63SCE</t>
+          <t>N041A45037</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SCRIPPS MEMORIAL HOSPITAL ENCINITAS</t>
+          <t>UNIVERSITY OF MISSISSIPPI MEDICAL CTR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>354 SANTA FE DRIVE</t>
+          <t>2500 NORTH STATE STREET</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ENCINITAS</t>
+          <t>JACKSON</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92024</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1514,99 +1517,99 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I23">
-        <v>193</v>
+        <v>697</v>
       </c>
       <c r="J23">
-        <v>4496</v>
+        <v>23438</v>
       </c>
       <c r="K23">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N007000115</t>
+          <t>N022ABN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CANYON VISTA MEDICAL CENTER</t>
+          <t>ABINGTON HOSPITAL - JEFFERSON HEALTH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>151-B COLONIA DE SALUD</t>
+          <t>1200 OLD YORK ROAD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SIERRA VISTA</t>
+          <t>ABINGTON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>85635-8225</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>655</v>
       </c>
       <c r="J24">
-        <v>3911</v>
+        <v>13688</v>
       </c>
       <c r="K24">
-        <v>0.09</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N007000125</t>
+          <t>N003B4MCMA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TUCSON MEDICAL CENTER</t>
+          <t>ATRIUM HEALTH NAVICENT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PO BOX 30400</t>
+          <t>777 HEMLOCK STREET</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TUCSON</t>
+          <t>MACON</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>85751</t>
+          <t>31201</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1616,48 +1619,48 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I25">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="J25">
-        <v>21254</v>
+        <v>24828</v>
       </c>
       <c r="K25">
-        <v>0.02</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>N009B6NPLT</t>
+          <t>N0122120</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GREAT PLAINS HEALTH</t>
+          <t>CAPE FEAR VALLEY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>601 W LEOTA STREET</t>
+          <t>BOX 2000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NORTH PLATTE</t>
+          <t>FAYETTEVILLE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1671,44 +1674,44 @@
         </is>
       </c>
       <c r="I26">
-        <v>116</v>
+        <v>634</v>
       </c>
       <c r="J26">
-        <v>3807</v>
+        <v>14424</v>
       </c>
       <c r="K26">
-        <v>0.18</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N011B1BARN</t>
+          <t>N003B1KENN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BARNES-JEWISH HOSPITAL</t>
+          <t>WELLSTAR KENNESTONE HOSPITAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 BARNES-JEWISH HOSPITAL PLAZA</t>
+          <t>677 CHURCH STREET</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAINT LOUIS</t>
+          <t>MARIETTA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1722,44 +1725,44 @@
         </is>
       </c>
       <c r="I27">
-        <v>1431</v>
+        <v>633</v>
       </c>
       <c r="J27">
-        <v>38697</v>
+        <v>24159</v>
       </c>
       <c r="K27">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N011B1CHNE</t>
+          <t>N007000125</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHRISTIAN HOSPITAL</t>
+          <t>TUCSON MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SITEMAN CANCER CTR AT NW</t>
+          <t>PO BOX 30400</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FLORISSANT</t>
+          <t>TUCSON</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>63031</t>
+          <t>85751</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1773,44 +1776,44 @@
         </is>
       </c>
       <c r="I28">
-        <v>482</v>
+        <v>629</v>
       </c>
       <c r="J28">
-        <v>5796</v>
+        <v>21254</v>
       </c>
       <c r="K28">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N011B5CARB</t>
+          <t>N0122490</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEMORIAL HOSPITAL-CARBONDALE</t>
+          <t>NOVANT HEALTH PRESBYTERIAN MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PO BOX 3988</t>
+          <t>301 HAWTHORNE LN #100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CARBONDALE</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1820,48 +1823,48 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I29">
-        <v>154</v>
+        <v>624</v>
       </c>
       <c r="J29">
-        <v>7584</v>
+        <v>23063</v>
       </c>
       <c r="K29">
-        <v>1.82</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>N011B9CMEC</t>
+          <t>N0337018</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CENTERPOINT MEDICAL CENTER</t>
+          <t>SAINT FRANCIS HOSPITAL AND MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19600 E 39TH ST</t>
+          <t>C/O TRINITY HEALTH EAST</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INDEPENDENCE</t>
+          <t>TROY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>64057</t>
+          <t>48007-7007</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1875,49 +1878,49 @@
         </is>
       </c>
       <c r="I30">
-        <v>285</v>
+        <v>617</v>
       </c>
       <c r="J30">
-        <v>10942</v>
+        <v>28498</v>
       </c>
       <c r="K30">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N011B9OVER</t>
+          <t>N022XRW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OVERLAND PARK REGIONAL MEDICAL CENTER</t>
+          <t>ROBERT WOOD JOHNSON UNIV HOSPITAL - NEW BRUNSWICK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10500 QUIVIRA ROAD</t>
+          <t>1 ROBERT WOOD JOHNSON PLACE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OVERLAND PARK</t>
+          <t>NEW BRUNSWICK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>66215</t>
+          <t>08903</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1926,44 +1929,44 @@
         </is>
       </c>
       <c r="I31">
-        <v>351</v>
+        <v>614</v>
       </c>
       <c r="J31">
-        <v>13366</v>
+        <v>19524</v>
       </c>
       <c r="K31">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>N0122120</t>
+          <t>N035N1UNVA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAPE FEAR VALLEY MEDICAL CENTER</t>
+          <t>UNIVERSITY OF VIRGINIA MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOX 2000</t>
+          <t>1215 LEE STREET ROOM 2801</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FAYETTEVILLE</t>
+          <t>CHARLOTTESVILLE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1973,48 +1976,48 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I32">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="J32">
-        <v>14424</v>
+        <v>26944</v>
       </c>
       <c r="K32">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>N0122225</t>
+          <t>N053B1GTWN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DUMC DUKE UNIVERSITY MEDICAL CENTER</t>
+          <t>GEORGETOWN UNIV HOSPITAL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2301 ERWIN ROAD</t>
+          <t>C/O MEDSTAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DURHAM</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>21236-6200</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2028,49 +2031,49 @@
         </is>
       </c>
       <c r="I33">
-        <v>960</v>
+        <v>609</v>
       </c>
       <c r="J33">
-        <v>38334</v>
+        <v>15511</v>
       </c>
       <c r="K33">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>N0122415</t>
+          <t>N003B6PMID</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NEW HANOVER REGIONAL MED CTR</t>
+          <t>PIEDMONT COLUMBUS REGIONAL MIDTOWN HOSP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PO BOX 1649</t>
+          <t>710 CENTER STREET</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WILMINGTON</t>
+          <t>COLUMBUS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2079,44 +2082,44 @@
         </is>
       </c>
       <c r="I34">
-        <v>800</v>
+        <v>583</v>
       </c>
       <c r="J34">
-        <v>28039</v>
+        <v>11941</v>
       </c>
       <c r="K34">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>N0122425</t>
+          <t>N02911027</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UNC MEDICAL CENTER</t>
+          <t>RIVERSIDE REGIONAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>101 MANNING DRIVE</t>
+          <t>608 DENBIGH BLVD SUITE 703</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHAPEL HILL</t>
+          <t>NEWPORT NEWS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2130,44 +2133,44 @@
         </is>
       </c>
       <c r="I35">
-        <v>923</v>
+        <v>576</v>
       </c>
       <c r="J35">
-        <v>30184</v>
+        <v>8322</v>
       </c>
       <c r="K35">
-        <v>0.87</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N0122490</t>
+          <t>N050B1STVS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NOVANT HEALTH PRESBYTERIAN MEDICAL CENTER</t>
+          <t>MERCY ST VINCENT MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>301 HAWTHORNE LN #100</t>
+          <t>2222 CHERRY STREET</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2177,53 +2180,53 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I36">
-        <v>624</v>
+        <v>568</v>
       </c>
       <c r="J36">
-        <v>23063</v>
+        <v>10387</v>
       </c>
       <c r="K36">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>N0122520</t>
+          <t>N022CHL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RUTHERFORD HOSPITAL INC</t>
+          <t>CHILDREN'S HOSPITAL OF PHILADELPHIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RUTHERFORD REG HEALTH SYS</t>
+          <t>PO BOX 2015</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>SECAUCUS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>37228</t>
+          <t>07096-2015</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2232,44 +2235,44 @@
         </is>
       </c>
       <c r="I37">
-        <v>143</v>
+        <v>564</v>
       </c>
       <c r="J37">
-        <v>3080</v>
+        <v>21019</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>N013B3SJOP</t>
+          <t>N0047128</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRINITY HEALTH OAKLAND HOSPITAL</t>
+          <t>UNIVERSITY OF VERMONT MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PO BOX 7007</t>
+          <t>111 COLCHESTER AVENUE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TROY</t>
+          <t>BURLINGTON</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>05401</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2283,44 +2286,44 @@
         </is>
       </c>
       <c r="I38">
-        <v>464</v>
+        <v>562</v>
       </c>
       <c r="J38">
-        <v>10680</v>
+        <v>22255</v>
       </c>
       <c r="K38">
-        <v>0.52</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>N013B5CMHC</t>
+          <t>N084B4MUIR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRINITY HEALTH ANN ARBOR HOSPITAL</t>
+          <t>JOHN MUIR MED CTR-WALNUT CREEK CAMPUS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TH#16105</t>
+          <t>1601 YGNACIO VALLEY ROAD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TROY</t>
+          <t>WALNUT CREEK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>48007-7007</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2334,49 +2337,49 @@
         </is>
       </c>
       <c r="I39">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="J39">
-        <v>22551</v>
+        <v>7592</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>N013B5UMMC</t>
+          <t>N030B7004H</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF MICHIGAN HOSPITALS</t>
+          <t>PENN STATE HEALTH MILTON S HERSHEY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1500 EAST MEDICAL CENTER DR</t>
+          <t>500 UNIVERSITY DRIVE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ANN ARBOR</t>
+          <t>HERSHEY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2385,49 +2388,49 @@
         </is>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>548</v>
       </c>
       <c r="J40">
-        <v>35336</v>
+        <v>30087</v>
       </c>
       <c r="K40">
-        <v>0.49</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>N016COL010</t>
+          <t>N040B0LOYO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MT CARMEL EAST HOSPITAL</t>
+          <t>LOYOLA UNIVERSITY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6001 EAST BROAD ST</t>
+          <t>2160 SOUTH FIRST AVENUE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>COLUMBUS</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>43213</t>
+          <t>60153</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2436,44 +2439,44 @@
         </is>
       </c>
       <c r="I41">
-        <v>400</v>
+        <v>547</v>
       </c>
       <c r="J41">
-        <v>12417</v>
+        <v>11852</v>
       </c>
       <c r="K41">
-        <v>1.39</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>N016COL012</t>
+          <t>N035B1LYNC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OHIO STATE UNIVERSITY WEXNER MEDICAL CENTER</t>
+          <t>LYNCHBURG GENERAL HOSPITAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>410 W 10TH AVE</t>
+          <t>1901 TATE SPRINGS ROAD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>COLUMBUS</t>
+          <t>LYNCHBURG</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>43210</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2487,44 +2490,44 @@
         </is>
       </c>
       <c r="I42">
-        <v>1106</v>
+        <v>534</v>
       </c>
       <c r="J42">
-        <v>24860</v>
+        <v>10752</v>
       </c>
       <c r="K42">
-        <v>0.01</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>N016COL013</t>
+          <t>N02911021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RIVERSIDE METHODIST HOSPITAL</t>
+          <t>SENTARA NORFOLK GENERAL HOSPITAL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3535 OLENTANGY RIVER RD</t>
+          <t>600 GRESHAM DRIVE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>COLUMBUS</t>
+          <t>NORFOLK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2538,44 +2541,44 @@
         </is>
       </c>
       <c r="I43">
-        <v>786</v>
+        <v>525</v>
       </c>
       <c r="J43">
-        <v>21606</v>
+        <v>20495</v>
       </c>
       <c r="K43">
-        <v>0.11</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>N016CTY017</t>
+          <t>N013B5CMHC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MANSFIELD HOSPITAL</t>
+          <t>TRINITY HEALTH ANN ARBOR HOSPITAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>335 GLESSNER AVE</t>
+          <t>TH#16105</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MANSFIELD</t>
+          <t>TROY</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>48007-7007</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2589,95 +2592,95 @@
         </is>
       </c>
       <c r="I44">
-        <v>368</v>
+        <v>524</v>
       </c>
       <c r="J44">
-        <v>5103</v>
+        <v>22551</v>
       </c>
       <c r="K44">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>N017STIL</t>
+          <t>N0031135</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAKEVIEW HOSPITAL</t>
+          <t>HCA-MEMORIAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>927 WEST CHURCHILL ST</t>
+          <t>4700 WATERS AVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>STILLWATER</t>
+          <t>SAVANNAH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>55082</t>
+          <t>31404-6220</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I45">
-        <v>97</v>
+        <v>512</v>
       </c>
       <c r="J45">
-        <v>7871</v>
+        <v>22050</v>
       </c>
       <c r="K45">
-        <v>1.61</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>N019058000</t>
+          <t>N035B1GALE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VANDERBILT UNIVERSITY MEDICAL CENTER</t>
+          <t>HCA-LEWIS GALE HOSPITAL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1301 MEDICAL CENTER DRIVE</t>
+          <t>1900 ELECTRIC ROAD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>SALEM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>24153</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2687,96 +2690,99 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I46">
-        <v>1025</v>
+        <v>506</v>
       </c>
       <c r="J46">
-        <v>50744</v>
+        <v>11402</v>
       </c>
       <c r="K46">
-        <v>1.65</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>N020LVMCFH</t>
+          <t>N011B1CHNE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MIKE OCALLAGHAN FEDERAL HOSPITAL</t>
+          <t>CHRISTIAN HOSPITAL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4700 LAS VEGAS BLVD N</t>
+          <t>SITEMAN CANCER CTR AT NW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NELLIS AFB</t>
+          <t>FLORISSANT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>89191</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I47">
-        <v>114</v>
+        <v>482</v>
+      </c>
+      <c r="J47">
+        <v>5796</v>
       </c>
       <c r="K47">
-        <v>1.32</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>N020LVSHMC</t>
+          <t>N053B1HOWD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SUNRISE HOSPITAL &amp; MED CTR</t>
+          <t>HOWARD UNIVERSITY HOSPITAL CORP.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3186 SOUTH MARYLAND PKWY</t>
+          <t>2041 GEORGIA AVE NW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LAS VEGAS</t>
+          <t>WASHINGTON</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2790,44 +2796,44 @@
         </is>
       </c>
       <c r="I48">
-        <v>762</v>
+        <v>482</v>
       </c>
       <c r="J48">
-        <v>17255</v>
+        <v>10016</v>
       </c>
       <c r="K48">
-        <v>1.83</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>N021P00010</t>
+          <t>N006BZRIVE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PORTLAND ADVENTIST MEDICAL CENTER</t>
+          <t>RIVERSIDE COMMUNITY HOSPITAL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10123 S.E. MARKET STREET</t>
+          <t>PO BOX 788</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PORTLAND</t>
+          <t>KAYSVILLE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>97216</t>
+          <t>84037</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2841,44 +2847,44 @@
         </is>
       </c>
       <c r="I49">
-        <v>302</v>
+        <v>478</v>
       </c>
       <c r="J49">
-        <v>10069</v>
+        <v>7760</v>
       </c>
       <c r="K49">
-        <v>0.09</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>N021P00306</t>
+          <t>N027B9CAMC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SALEM HEALTH</t>
+          <t>CHARLESTON AREA MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>890 OAK STREET SE</t>
+          <t>PO BOX 2069</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SALEM</t>
+          <t>CHARLESTON</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>WV</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>97301</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2892,44 +2898,41 @@
         </is>
       </c>
       <c r="I50">
-        <v>454</v>
-      </c>
-      <c r="J50">
-        <v>13817</v>
+        <v>472</v>
       </c>
       <c r="K50">
-        <v>1.14</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>N021P00503</t>
+          <t>N013B3SJOP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GOOD SAMARITAN HOSPITAL-CORVALLIS</t>
+          <t>TRINITY HEALTH OAKLAND HOSPITAL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PO BOX 3000</t>
+          <t>PO BOX 7007</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CORVALLIS</t>
+          <t>TROY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>97339-3000</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2943,44 +2946,44 @@
         </is>
       </c>
       <c r="I51">
-        <v>188</v>
+        <v>464</v>
       </c>
       <c r="J51">
-        <v>10872</v>
+        <v>10680</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>N022ABN</t>
+          <t>N024001090</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ABINGTON HOSPITAL - JEFFERSON HEALTH</t>
+          <t>ST VINCENT EVANSVILLE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1200 OLD YORK ROAD</t>
+          <t>3700 WASHINGTON AVENUE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ABINGTON</t>
+          <t>EVANSVILLE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>47715</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2994,95 +2997,95 @@
         </is>
       </c>
       <c r="I52">
-        <v>655</v>
+        <v>463</v>
       </c>
       <c r="J52">
-        <v>13688</v>
+        <v>23241</v>
       </c>
       <c r="K52">
-        <v>0.8100000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N022CHL</t>
+          <t>N021P00306</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CHILDREN'S HOSPITAL OF PHILADELPHIA</t>
+          <t>SALEM HEALTH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PO BOX 2015</t>
+          <t>890 OAK STREET SE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SECAUCUS</t>
+          <t>SALEM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>07096-2015</t>
+          <t>97301</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I53">
-        <v>564</v>
+        <v>454</v>
       </c>
       <c r="J53">
-        <v>21019</v>
+        <v>13817</v>
       </c>
       <c r="K53">
-        <v>0.02</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>N022LOL</t>
+          <t>N006B9RRMC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIRTUA HEALTH CAMDEN</t>
+          <t>RONALD REAGAN UCLA MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1600 HADDON AVENUE</t>
+          <t>757 WESTWOOD BLVD</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CAMDEN</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>08103</t>
+          <t>90095</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3092,53 +3095,53 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I54">
-        <v>340</v>
+        <v>446</v>
       </c>
       <c r="J54">
-        <v>10764</v>
+        <v>23644</v>
       </c>
       <c r="K54">
-        <v>0.83</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>N022LVHM</t>
+          <t>N049T3301T</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LEHIGH VALLEY HOSPITAL - MUHLENBERG</t>
+          <t>MEDICAL CITY ARLINGTON</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2545 SCHOENERSVILLE RD</t>
+          <t>3301 MATLOCK DRIVE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BETHLEHEM</t>
+          <t>ARLINGTON</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>76015</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3147,44 +3150,44 @@
         </is>
       </c>
       <c r="I55">
-        <v>256</v>
+        <v>431</v>
       </c>
       <c r="J55">
-        <v>10439</v>
+        <v>4174</v>
       </c>
       <c r="K55">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>N022NJCITY</t>
+          <t>N006B3UCIM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JERSEY CITY MEDICAL CENTER</t>
+          <t>UNIVERSITY OF CALIFORNIA, IRVINE MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>355 GRAND STREET</t>
+          <t>PO BOX C11917</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JERSEY CITY</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>07302</t>
+          <t>92711</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3198,44 +3201,44 @@
         </is>
       </c>
       <c r="I56">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="J56">
-        <v>7679</v>
+        <v>12748</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>N022SCHB</t>
+          <t>N016COL010</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ST CHRISTOPHER'S HOSP FOR CHILDREN/ TOWER HEALTH SYSTEM</t>
+          <t>MT CARMEL EAST HOSPITAL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PO BOX 26968</t>
+          <t>6001 EAST BROAD ST</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PHILADELPHIA</t>
+          <t>COLUMBUS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>43213</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3245,48 +3248,48 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I57">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="J57">
-        <v>22519</v>
+        <v>12417</v>
       </c>
       <c r="K57">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>N022TEM</t>
+          <t>N084B5DMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TEMPLE UNIVERSITY HOSPITAL</t>
+          <t>DOCTORS MEDICAL CENTER OF MODESTO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3401 N BROAD STREET</t>
+          <t>PO BOX 925</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PHILADELPHIA</t>
+          <t>CHESTERTON</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>46304</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3300,95 +3303,92 @@
         </is>
       </c>
       <c r="I58">
-        <v>732</v>
-      </c>
-      <c r="J58">
-        <v>30008</v>
+        <v>394</v>
       </c>
       <c r="K58">
-        <v>1.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>N022WTD</t>
+          <t>N006BJANVD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JEFFERSON WASHINGTON TOWNSHIP HOSPITAL</t>
+          <t>ANTELOPE VALLEY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PO BOX 5085</t>
+          <t>1600 WEST AVENUE J</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CHERRY HILL</t>
+          <t>LANCASTER</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>08034-5085</t>
+          <t>93534</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I59">
-        <v>230</v>
+        <v>390</v>
       </c>
       <c r="J59">
-        <v>15738</v>
+        <v>12259</v>
       </c>
       <c r="K59">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>N022XRW</t>
+          <t>N055B3BERN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ROBERT WOOD JOHNSON UNIV HOSPITAL - NEW BRUNSWICK</t>
+          <t>ST BERNARDS MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 ROBERT WOOD JOHNSON PLACE</t>
+          <t>224 E WASHINGTON</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NEW BRUNSWICK</t>
+          <t>JONESBORO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>08903</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3398,48 +3398,48 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I60">
-        <v>614</v>
+        <v>378</v>
       </c>
       <c r="J60">
-        <v>19524</v>
+        <v>10197</v>
       </c>
       <c r="K60">
-        <v>1.71</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>N022XWC</t>
+          <t>N016CTY017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CHRISTIANA CARE HEALTH SERVICES, INC</t>
+          <t>MANSFIELD HOSPITAL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PO BOX 2653</t>
+          <t>335 GLESSNER AVE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>WILMINGTON</t>
+          <t>MANSFIELD</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>44903</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3453,41 +3453,44 @@
         </is>
       </c>
       <c r="I61">
-        <v>906</v>
+        <v>368</v>
+      </c>
+      <c r="J61">
+        <v>5103</v>
       </c>
       <c r="K61">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>N024001040</t>
+          <t>N027B2LTUN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BLOOMINGTON HOSPITAL</t>
+          <t>UPMC ALTOONA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2651 E DISCOVERY PARKWAY</t>
+          <t>UPMC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BLOOMINGTON</t>
+          <t>PORTLAND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>47408</t>
+          <t>97208</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3497,99 +3500,99 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I62">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="J62">
-        <v>8099</v>
+        <v>26076</v>
       </c>
       <c r="K62">
-        <v>0.89</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>N024001090</t>
+          <t>N006BNCEVC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ST VINCENT EVANSVILLE</t>
+          <t>CENTINELA HOSPITAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3700 WASHINGTON AVENUE</t>
+          <t>555 EAST HARDY STREET</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EVANSVILLE</t>
+          <t>INGLEWOOD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>47715</t>
+          <t>90301</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I63">
-        <v>463</v>
+        <v>362</v>
       </c>
       <c r="J63">
-        <v>23241</v>
+        <v>2035</v>
       </c>
       <c r="K63">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>N027B2LTUN</t>
+          <t>N024001040</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UPMC ALTOONA</t>
+          <t>BLOOMINGTON HOSPITAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UPMC</t>
+          <t>2651 E DISCOVERY PARKWAY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PORTLAND</t>
+          <t>BLOOMINGTON</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3599,48 +3602,48 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I64">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="J64">
-        <v>26076</v>
+        <v>8099</v>
       </c>
       <c r="K64">
-        <v>0.11</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>N027B8TMCB</t>
+          <t>N011B9OVER</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HERITAGE VALLEY BEAVER</t>
+          <t>OVERLAND PARK REGIONAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1000 DUTCH RIDGE ROAD</t>
+          <t>10500 QUIVIRA ROAD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BEAVER</t>
+          <t>OVERLAND PARK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3654,44 +3657,44 @@
         </is>
       </c>
       <c r="I65">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="J65">
-        <v>14576</v>
+        <v>13366</v>
       </c>
       <c r="K65">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>N027B9CAMC</t>
+          <t>N022NJCITY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CHARLESTON AREA MEDICAL CENTER</t>
+          <t>JERSEY CITY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PO BOX 2069</t>
+          <t>355 GRAND STREET</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>JERSEY CITY</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>07302</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3705,41 +3708,44 @@
         </is>
       </c>
       <c r="I66">
-        <v>472</v>
+        <v>348</v>
+      </c>
+      <c r="J66">
+        <v>7679</v>
       </c>
       <c r="K66">
-        <v>0.77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>N027CABH</t>
+          <t>N053B0SNAI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CABELL HUNTINGTON HOSPITAL</t>
+          <t>SINAI HOSPITAL-BALTIMORE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1340 HAL GREER BLVD</t>
+          <t>2401 WEST BELVEDERE AVENUE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HUNTINGTON</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3753,44 +3759,44 @@
         </is>
       </c>
       <c r="I67">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="J67">
-        <v>14974</v>
+        <v>19486</v>
       </c>
       <c r="K67">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>N027CAML</t>
+          <t>N022LOL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CAMDEN CLARK HOSPITAL</t>
+          <t>VIRTUA HEALTH CAMDEN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>800 GARFIELD AVENUE</t>
+          <t>1600 HADDON AVENUE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PARKERSBURG</t>
+          <t>CAMDEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>08103</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3804,44 +3810,44 @@
         </is>
       </c>
       <c r="I68">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="J68">
-        <v>17478</v>
+        <v>10764</v>
       </c>
       <c r="K68">
-        <v>0.03</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>N027S0WASH</t>
+          <t>N003B1SRMC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MERITUS MEDICAL CENTER</t>
+          <t>SOUTHERN REGIONAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11116 MEDICAL CAMPUS ROAD</t>
+          <t>3480 E GUASTI ROAD 2ND FLOOR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>HAGERSTOWN</t>
+          <t>ONTARIO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3855,10 +3861,10 @@
         </is>
       </c>
       <c r="I69">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="J69">
-        <v>8274</v>
+        <v>8193</v>
       </c>
       <c r="K69">
         <v>1.53</v>
@@ -3867,32 +3873,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>N02911021</t>
+          <t>N050B1MCOH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SENTARA NORFOLK GENERAL HOSPITAL</t>
+          <t>UNIVERSITY OF TOLEDO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>600 GRESHAM DRIVE</t>
+          <t>2801 WEST BANCROFT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>43606-3390</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3906,44 +3912,44 @@
         </is>
       </c>
       <c r="I70">
-        <v>525</v>
+        <v>319</v>
       </c>
       <c r="J70">
-        <v>20495</v>
+        <v>9840</v>
       </c>
       <c r="K70">
-        <v>1.45</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>N02911027</t>
+          <t>N027CABH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RIVERSIDE REGIONAL MEDICAL CENTER</t>
+          <t>CABELL HUNTINGTON HOSPITAL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>608 DENBIGH BLVD SUITE 703</t>
+          <t>1340 HAL GREER BLVD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NEWPORT NEWS</t>
+          <t>HUNTINGTON</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3957,34 +3963,34 @@
         </is>
       </c>
       <c r="I71">
-        <v>576</v>
+        <v>313</v>
       </c>
       <c r="J71">
-        <v>8322</v>
+        <v>14974</v>
       </c>
       <c r="K71">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>N02912034</t>
+          <t>N02913003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SENTARA WILLIAMSBURG REGIONAL MED CENTER</t>
+          <t>CHESAPEAKE REGIONAL MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C/O SENTARA NORFOLK GEN HOSP</t>
+          <t>736 N BATTLEFIELD BLVD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>CHESAPEAKE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3994,7 +4000,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4008,44 +4014,44 @@
         </is>
       </c>
       <c r="I72">
-        <v>145</v>
+        <v>310</v>
       </c>
       <c r="J72">
-        <v>5016</v>
+        <v>16138</v>
       </c>
       <c r="K72">
-        <v>1.8</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>N02913003</t>
+          <t>N021P00010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CHESAPEAKE REGIONAL MEDICAL CENTER</t>
+          <t>PORTLAND ADVENTIST MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>736 N BATTLEFIELD BLVD</t>
+          <t>10123 S.E. MARKET STREET</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CHESAPEAKE</t>
+          <t>PORTLAND</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>97216</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4055,48 +4061,48 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I73">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J73">
-        <v>16138</v>
+        <v>10069</v>
       </c>
       <c r="K73">
-        <v>0.41</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N030B31001</t>
+          <t>N027CAML</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUTHRIE ROBERT PACKER HOSPITAL</t>
+          <t>CAMDEN CLARK HOSPITAL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ONE GUTHRIE SQUARE</t>
+          <t>800 GARFIELD AVENUE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAYRE</t>
+          <t>PARKERSBURG</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>WV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4106,48 +4112,48 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I74">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="J74">
-        <v>36613</v>
+        <v>17478</v>
       </c>
       <c r="K74">
-        <v>0.82</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>N030B7004H</t>
+          <t>N049T1650T</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PENN STATE HEALTH MILTON S HERSHEY MEDICAL CENTER</t>
+          <t>BAYLOR SCOTT AND WHITE MED CTR-GRAPEVINE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>500 UNIVERSITY DRIVE</t>
+          <t>1650 WEST COLLEGE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HERSHEY</t>
+          <t>GRAPEVINE</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>76051</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4161,44 +4167,44 @@
         </is>
       </c>
       <c r="I75">
-        <v>548</v>
+        <v>302</v>
       </c>
       <c r="J75">
-        <v>30087</v>
+        <v>7001</v>
       </c>
       <c r="K75">
-        <v>1.83</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>N0337018</t>
+          <t>N011B9CMEC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAINT FRANCIS HOSPITAL AND MEDICAL CENTER</t>
+          <t>CENTERPOINT MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C/O TRINITY HEALTH EAST</t>
+          <t>19600 E 39TH ST</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TROY</t>
+          <t>INDEPENDENCE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>48007-7007</t>
+          <t>64057</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4212,95 +4218,95 @@
         </is>
       </c>
       <c r="I76">
-        <v>617</v>
+        <v>285</v>
       </c>
       <c r="J76">
-        <v>28498</v>
+        <v>10942</v>
       </c>
       <c r="K76">
-        <v>1.94</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>N035B1GALE</t>
+          <t>N027B8TMCB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HCA-LEWIS GALE HOSPITAL</t>
+          <t>HERITAGE VALLEY BEAVER</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1900 ELECTRIC ROAD</t>
+          <t>1000 DUTCH RIDGE ROAD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SALEM</t>
+          <t>BEAVER</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I77">
-        <v>506</v>
+        <v>285</v>
       </c>
       <c r="J77">
-        <v>11402</v>
+        <v>14576</v>
       </c>
       <c r="K77">
-        <v>0.98</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>N035B1LYNC</t>
+          <t>N053B0NOAR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LYNCHBURG GENERAL HOSPITAL</t>
+          <t>UMMS-BALTIMORE WASHINGTON MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1901 TATE SPRINGS ROAD</t>
+          <t>301 HOSPITAL DRIVE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LYNCHBURG</t>
+          <t>GLEN BURNIE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4310,48 +4316,48 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I78">
-        <v>534</v>
+        <v>285</v>
       </c>
       <c r="J78">
-        <v>10752</v>
+        <v>11624</v>
       </c>
       <c r="K78">
-        <v>1.36</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>N035CCLB</t>
+          <t>N049T4500T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CARILION CONSOLIDATED LABS</t>
+          <t>MEDICAL CITY OF MCKINNEY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PO BOX 13367</t>
+          <t>4500 MEDICAL CENTER DRIVE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ROANOKE</t>
+          <t>MCKINNEY</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>75069</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4365,49 +4371,49 @@
         </is>
       </c>
       <c r="I79">
-        <v>737</v>
+        <v>257</v>
       </c>
       <c r="J79">
-        <v>25834</v>
+        <v>4955</v>
       </c>
       <c r="K79">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>N035N1UNVA</t>
+          <t>N022LVHM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF VIRGINIA MEDICAL CENTER</t>
+          <t>LEHIGH VALLEY HOSPITAL - MUHLENBERG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1215 LEE STREET ROOM 2801</t>
+          <t>2545 SCHOENERSVILLE RD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CHARLOTTESVILLE</t>
+          <t>BETHLEHEM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4416,44 +4422,44 @@
         </is>
       </c>
       <c r="I80">
-        <v>612</v>
+        <v>256</v>
       </c>
       <c r="J80">
-        <v>26944</v>
+        <v>10439</v>
       </c>
       <c r="K80">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N035N1VCU</t>
+          <t>N030B31001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VCU MEDICAL CENTER</t>
+          <t>GUTHRIE ROBERT PACKER HOSPITAL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>800 EAST LEIGH STREET STE 212</t>
+          <t>ONE GUTHRIE SQUARE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RICHMOND</t>
+          <t>SAYRE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4467,44 +4473,44 @@
         </is>
       </c>
       <c r="I81">
-        <v>811</v>
+        <v>254</v>
       </c>
       <c r="J81">
-        <v>28758</v>
+        <v>36613</v>
       </c>
       <c r="K81">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N036B1MUSC</t>
+          <t>N038B7METI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MEDICAL UNIVERSITY OF SC</t>
+          <t>RILEY HOSPITAL FOR CHILDREN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MUSC HEMAPHERESIS</t>
+          <t>350 W 11TH STREET</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>INDIANAPOLIS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4518,34 +4524,31 @@
         </is>
       </c>
       <c r="I82">
-        <v>713</v>
-      </c>
-      <c r="J82">
-        <v>36299</v>
+        <v>250</v>
       </c>
       <c r="K82">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>N036B1WACC</t>
+          <t>N036B2VACO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIDELANDS WACCAMAW COMMUNITY HOSPITAL</t>
+          <t>VAMC COLUMBIA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4070 HIGHWAY 17 BYPASS</t>
+          <t>6439 GARNER'S FERRY ROAD</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MURRELLS INLET</t>
+          <t>COLUMBIA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4555,7 +4558,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>29209</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4569,44 +4572,44 @@
         </is>
       </c>
       <c r="I83">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="J83">
-        <v>7779</v>
+        <v>3534</v>
       </c>
       <c r="K83">
-        <v>0.53</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N036B2VACO</t>
+          <t>N001003102</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VAMC COLUMBIA</t>
+          <t>GUTHRIE LOURDES HOSPITAL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6439 GARNER'S FERRY ROAD</t>
+          <t>ASCENSION HLTH MINISTRY SRV CT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>COLUMBIA</t>
+          <t>INDIANAPOLIS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>29209</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4616,48 +4619,48 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I84">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J84">
-        <v>3534</v>
+        <v>18194</v>
       </c>
       <c r="K84">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>N038B7METI</t>
+          <t>N027S0WASH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RILEY HOSPITAL FOR CHILDREN</t>
+          <t>MERITUS MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>350 W 11TH STREET</t>
+          <t>11116 MEDICAL CAMPUS ROAD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS</t>
+          <t>HAGERSTOWN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4667,147 +4670,150 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I85">
-        <v>250</v>
+        <v>237</v>
+      </c>
+      <c r="J85">
+        <v>8274</v>
       </c>
       <c r="K85">
-        <v>0.6</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N040B0ADVC</t>
+          <t>N022WTD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADVOCATE CHRIST MEDICAL CENTER</t>
+          <t>JEFFERSON WASHINGTON TOWNSHIP HOSPITAL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4440 W 95TH ST</t>
+          <t>PO BOX 5085</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OAK LAWN</t>
+          <t>CHERRY HILL</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>08034-5085</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I86">
-        <v>802</v>
+        <v>230</v>
       </c>
       <c r="J86">
-        <v>21518</v>
+        <v>15738</v>
       </c>
       <c r="K86">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N040B0LOYO</t>
+          <t>N006BZKONT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LOYOLA UNIVERSITY MEDICAL CENTER</t>
+          <t>KAISER PERMANENTE ONTARIO MED CTR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2160 SOUTH FIRST AVENUE</t>
+          <t>2295 SOUTH VINEYARD AVENUE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>ONTARIO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I87">
-        <v>547</v>
+        <v>224</v>
       </c>
       <c r="J87">
-        <v>11852</v>
+        <v>17033</v>
       </c>
       <c r="K87">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N041A45037</t>
+          <t>N0047369</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF MISSISSIPPI MEDICAL CTR</t>
+          <t>HCA-PORTSMOUTH HOSPITAL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2500 NORTH STATE STREET</t>
+          <t>333 BORTHWICK AVENUE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JACKSON</t>
+          <t>PORTSMOUTH</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>03801</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4821,100 +4827,100 @@
         </is>
       </c>
       <c r="I88">
-        <v>697</v>
+        <v>220</v>
       </c>
       <c r="J88">
-        <v>23438</v>
+        <v>12274</v>
       </c>
       <c r="K88">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N049T0062C</t>
+          <t>N006B3HUWA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BAYLOR UNIVERSITY MEDICAL CTR AT DALLAS</t>
+          <t>WEST ANAHEIM MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3500 GASTON AVENUE</t>
+          <t>3033 WEST ORANGE AVENUE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DALLAS</t>
+          <t>ANAHEIM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>75246</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I89">
-        <v>914</v>
+        <v>219</v>
       </c>
       <c r="J89">
-        <v>20997</v>
+        <v>1077</v>
       </c>
       <c r="K89">
-        <v>1.94</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N049T0300F</t>
+          <t>N053B1BNMC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BAYLOR SCOTT AND WHITE MEDICAL CTR-PLANO</t>
+          <t>WALTER REED NATIONAL MILITARY MED CTR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4700 ALLIANCE BLVD</t>
+          <t>8901 WISCONSIN AVENUE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PLANO</t>
+          <t>BETHESDA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>75093</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4923,95 +4929,92 @@
         </is>
       </c>
       <c r="I90">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="J90">
-        <v>6165</v>
+        <v>10191</v>
       </c>
       <c r="K90">
-        <v>0.11</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N049T1650T</t>
+          <t>N006BZPKVW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BAYLOR SCOTT AND WHITE MED CTR-GRAPEVINE</t>
+          <t>DOCTORS HOSPITAL OF RIVERSIDE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1650 WEST COLLEGE</t>
+          <t>3865 JACKSON ST</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GRAPEVINE</t>
+          <t>RIVERSIDE</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>92503</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I91">
-        <v>302</v>
-      </c>
-      <c r="J91">
-        <v>7001</v>
+        <v>193</v>
       </c>
       <c r="K91">
-        <v>0.5</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N049T3301T</t>
+          <t>N006E63SCE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MEDICAL CITY ARLINGTON</t>
+          <t>SCRIPPS MEMORIAL HOSPITAL ENCINITAS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3301 MATLOCK DRIVE</t>
+          <t>354 SANTA FE DRIVE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ARLINGTON</t>
+          <t>ENCINITAS</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>76015</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5021,48 +5024,48 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I92">
-        <v>431</v>
+        <v>193</v>
       </c>
       <c r="J92">
-        <v>4174</v>
+        <v>4496</v>
       </c>
       <c r="K92">
-        <v>1.57</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N049T4500T</t>
+          <t>N021P00503</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MEDICAL CITY OF MCKINNEY</t>
+          <t>GOOD SAMARITAN HOSPITAL-CORVALLIS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>4500 MEDICAL CENTER DRIVE</t>
+          <t>PO BOX 3000</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MCKINNEY</t>
+          <t>CORVALLIS</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>75069</t>
+          <t>97339-3000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5076,49 +5079,49 @@
         </is>
       </c>
       <c r="I93">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="J93">
-        <v>4955</v>
+        <v>10872</v>
       </c>
       <c r="K93">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N049T5252T</t>
+          <t>N022SCHB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BAYLOR SCOTT AND WHITE MED CTR-MCKINNEY</t>
+          <t>ST CHRISTOPHER'S HOSP FOR CHILDREN/ TOWER HEALTH SYSTEM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5252 W UNIVERSITY BLVD</t>
+          <t>PO BOX 26968</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MCKINNEY</t>
+          <t>PHILADELPHIA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>75071</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5127,41 +5130,44 @@
         </is>
       </c>
       <c r="I94">
-        <v>143</v>
+        <v>188</v>
+      </c>
+      <c r="J94">
+        <v>22519</v>
       </c>
       <c r="K94">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N050B1MCOH</t>
+          <t>N0042003</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF TOLEDO</t>
+          <t>VA MEDICAL CENTER WEST ROXBURY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2801 WEST BANCROFT</t>
+          <t>DEPT OF VETERANS AFFAIRS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>AUSTIN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>43606-3390</t>
+          <t>78714-9975</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5171,48 +5177,45 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I95">
-        <v>319</v>
-      </c>
-      <c r="J95">
-        <v>9840</v>
+        <v>172</v>
       </c>
       <c r="K95">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N050B1STVS</t>
+          <t>N049T0300F</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MERCY ST VINCENT MEDICAL CENTER</t>
+          <t>BAYLOR SCOTT AND WHITE MEDICAL CTR-PLANO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2222 CHERRY STREET</t>
+          <t>4700 ALLIANCE BLVD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>PLANO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5222,53 +5225,53 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I96">
-        <v>568</v>
+        <v>160</v>
       </c>
       <c r="J96">
-        <v>10387</v>
+        <v>6165</v>
       </c>
       <c r="K96">
-        <v>0.78</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N053B0HOPK</t>
+          <t>N011B5CARB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JOHNS HOPKINS HOSPITAL</t>
+          <t>MEMORIAL HOSPITAL-CARBONDALE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PO BOX 5085</t>
+          <t>PO BOX 3988</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>CARBONDALE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5277,44 +5280,44 @@
         </is>
       </c>
       <c r="I97">
-        <v>1095</v>
+        <v>154</v>
       </c>
       <c r="J97">
-        <v>58423</v>
+        <v>7584</v>
       </c>
       <c r="K97">
-        <v>0.68</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N053B0NOAR</t>
+          <t>N02912034</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UMMS-BALTIMORE WASHINGTON MEDICAL CENTER</t>
+          <t>SENTARA WILLIAMSBURG REGIONAL MED CENTER</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>301 HOSPITAL DRIVE</t>
+          <t>C/O SENTARA NORFOLK GEN HOSP</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GLEN BURNIE</t>
+          <t>NORFOLK</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>21061</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5328,44 +5331,44 @@
         </is>
       </c>
       <c r="I98">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="J98">
-        <v>11624</v>
+        <v>5016</v>
       </c>
       <c r="K98">
-        <v>0.08</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N053B0SNAI</t>
+          <t>N0122520</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SINAI HOSPITAL-BALTIMORE</t>
+          <t>RUTHERFORD HOSPITAL INC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2401 WEST BELVEDERE AVENUE</t>
+          <t>RUTHERFORD REG HEALTH SYS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5375,144 +5378,147 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I99">
-        <v>348</v>
+        <v>143</v>
       </c>
       <c r="J99">
-        <v>19486</v>
+        <v>3080</v>
       </c>
       <c r="K99">
-        <v>0.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N053B1BNMC</t>
+          <t>N049T5252T</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WALTER REED NATIONAL MILITARY MED CTR</t>
+          <t>BAYLOR SCOTT AND WHITE MED CTR-MCKINNEY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8901 WISCONSIN AVENUE</t>
+          <t>5252 W UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BETHESDA</t>
+          <t>MCKINNEY</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>75071</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I100">
-        <v>205</v>
-      </c>
-      <c r="J100">
-        <v>10191</v>
+        <v>143</v>
       </c>
       <c r="K100">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N053B1CAPR</t>
+          <t>N036B1WACC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>UM CAPITAL REGION MEDICAL CENTER</t>
+          <t>TIDELANDS WACCAMAW COMMUNITY HOSPITAL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>901 HENRY S TRUMAN DR N</t>
+          <t>4070 HIGHWAY 17 BYPASS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LARGO</t>
+          <t>MURRELLS INLET</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="I101">
+        <v>124</v>
+      </c>
+      <c r="J101">
+        <v>7779</v>
       </c>
       <c r="K101">
-        <v>1.56</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N053B1GTWN</t>
+          <t>N009B6NPLT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEORGETOWN UNIV HOSPITAL</t>
+          <t>GREAT PLAINS HEALTH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C/O MEDSTAR</t>
+          <t>601 W LEOTA STREET</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>NORTH PLATTE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>21236-6200</t>
+          <t>69101</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5522,155 +5528,152 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I102">
-        <v>609</v>
+        <v>116</v>
       </c>
       <c r="J102">
-        <v>15511</v>
+        <v>3807</v>
       </c>
       <c r="K102">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>N053B1HOWD</t>
+          <t>N020LVMCFH</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HOWARD UNIVERSITY HOSPITAL CORP.</t>
+          <t>MIKE OCALLAGHAN FEDERAL HOSPITAL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2041 GEORGIA AVE NW</t>
+          <t>4700 LAS VEGAS BLVD N</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WASHINGTON</t>
+          <t>NELLIS AFB</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>89191</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I103">
-        <v>482</v>
-      </c>
-      <c r="J103">
-        <v>10016</v>
+        <v>114</v>
       </c>
       <c r="K103">
-        <v>0.43</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N053B1WAHC</t>
+          <t>N007000115</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WASHINGTON HOSPITAL CENTER</t>
+          <t>CANYON VISTA MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C/O MEDSTAR</t>
+          <t>151-B COLONIA DE SALUD</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>SIERRA VISTA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>21236-6200</t>
+          <t>85635-8225</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I104">
-        <v>926</v>
+        <v>100</v>
       </c>
       <c r="J104">
-        <v>23505</v>
+        <v>3911</v>
       </c>
       <c r="K104">
-        <v>1.14</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N055B3BERN</t>
+          <t>N017STIL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ST BERNARDS MEDICAL CENTER</t>
+          <t>LAKEVIEW HOSPITAL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>224 E WASHINGTON</t>
+          <t>927 WEST CHURCHILL ST</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JONESBORO</t>
+          <t>STILLWATER</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>55082</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5679,34 +5682,34 @@
         </is>
       </c>
       <c r="I105">
-        <v>378</v>
+        <v>97</v>
       </c>
       <c r="J105">
-        <v>10197</v>
+        <v>7871</v>
       </c>
       <c r="K105">
-        <v>0.54</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N084B4MUIR</t>
+          <t>N006B0COLA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JOHN MUIR MED CTR-WALNUT CREEK CAMPUS</t>
+          <t>LOS ANGELES COMMUNITY HOSPITAL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1601 YGNACIO VALLEY ROAD</t>
+          <t>4081 EAST OLYMPIC BLVD</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WALNUT CREEK</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5716,75 +5719,72 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>94598</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I106">
-        <v>554</v>
+        <v>91</v>
       </c>
       <c r="J106">
-        <v>7592</v>
+        <v>1360</v>
       </c>
       <c r="K106">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>N084B5DMO</t>
+          <t>N053B1CAPR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DOCTORS MEDICAL CENTER OF MODESTO</t>
+          <t>UM CAPITAL REGION MEDICAL CENTER</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PO BOX 925</t>
+          <t>901 HENRY S TRUMAN DR N</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CHESTERTON</t>
+          <t>LARGO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I107">
-        <v>394</v>
+          <t>N</t>
+        </is>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="108">
